--- a/aq_files/0591.xlsx
+++ b/aq_files/0591.xlsx
@@ -1,195 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
-  <si>
-    <t>Stage_ID,Stage_Name,Job_Type,Input_Records,Output_Records,Processing_Time_Sec,CPU_Time_Sec,Memory_MB,Data_Local_Pct,Spill_Count,Combine_Records_In,Combine_Records_Out,Partition_Count,Shuffle_Data_MB,Sort_Time_Sec,Group_Time_Sec,Key_Count,Unique_Keys,Avg_Key_Size_Bytes,Avg_Value_Size_Bytes,Skew_Factor,Task_Count,Speculative_Runs,Failed_Attempts</t>
-  </si>
-  <si>
-    <t>MAP-001,WordCount_Mapper,Text_Processing,10000000,2500000,45,180,4096,92,12,2500000,450000,8,0,0,0,2500000,1800000,12,24,1.2,64,2,0</t>
-  </si>
-  <si>
-    <t>RED-001,WordCount_Reducer,Aggregation,2500000,1800000,28,112,8192,0,0,0,0,8,3200,8,15,1800000,1800000,12,24,1.3,8,1,0</t>
-  </si>
-  <si>
-    <t>MAP-002,LogParser_Mapper,ETL,20000000,9800000,92,368,8192,89,28,9800000,1890000,16,0,0,0,9800000,8200000,24,48,1.5,128,3,1</t>
-  </si>
-  <si>
-    <t>RED-002,LogParser_Reducer,ETL,9800000,6400000,56,224,16384,0,0,0,0,16,6500,12,18,6400000,6400000,24,48,1.4,16,2,0</t>
-  </si>
-  <si>
-    <t>MAP-003,SalesAgg_Mapper,Aggregation,5000000,1250000,38,152,4096,94,8,1250000,210000,4,0,0,0,1250000,950000,16,32,1.1,64,1,0</t>
-  </si>
-  <si>
-    <t>RED-003,SalesAgg_Reducer,Aggregation,1250000,320000,15,60,4096,0,0,0,0,4,1800,5,10,320000,320000,16,32,1.2,8,1,0</t>
-  </si>
-  <si>
-    <t>MAP-004,ClickStream_Mapper,Analytics,50000000,31500000,289,1156,16384,86,56,31500000,8250000,48,0,0,0,31500000,28500000,32,64,2.1,384,6,2</t>
-  </si>
-  <si>
-    <t>RED-004,ClickStream_Reducer,Analytics,31500000,16800000,168,672,32768,0,0,0,0,48,19200,22,28,16800000,16800000,32,64,2.2,48,3,1</t>
-  </si>
-  <si>
-    <t>MAP-005,UserSegment_Mapper,Segmentation,15000000,1890000,142,568,8192,91,34,1890000,315000,24,0,0,0,1890000,1560000,28,56,1.8,192,4,0</t>
-  </si>
-  <si>
-    <t>RED-005,UserSegment_Reducer,Segmentation,1890000,960000,84,336,12288,0,0,0,0,24,4800,14,19,960000,960000,28,56,1.6,24,2,0</t>
-  </si>
-  <si>
-    <t>MAP-006,FraudDetect_Mapper,Detection,80000000,21500000,378,1512,24576,84,78,21500000,890000,64,0,0,0,21500000,19800000,48,96,2.8,512,8,3</t>
-  </si>
-  <si>
-    <t>RED-006,FraudDetect_Reducer,Detection,21500000,1600000,45,180,16384,0,0,0,0,64,12800,18,25,1600000,1600000,48,96,2.5,8,2,1</t>
-  </si>
-  <si>
-    <t>MAP-007,PageRank_Mapper,Graph,12000000,12000000,98,392,8192,88,18,12000000,12000000,128,0,0,0,12000000,8500000,64,128,1.4,128,2,0</t>
-  </si>
-  <si>
-    <t>RED-007,PageRank_Reducer,Graph,12000000,12000000,245,980,32768,0,0,0,0,128,12800,45,56,12000000,12000000,64,128,1.5,128,4,1</t>
-  </si>
-  <si>
-    <t>MAP-008,ImageProcess_Mapper,Image,5000000,2500000,756,3024,49152,82,95,2500000,1250000,128,0,0,0,2500000,2100000,512,1024,3.2,1024,12,4</t>
-  </si>
-  <si>
-    <t>RED-008,ImageProcess_Reducer,Image,2500000,1250000,504,2016,65536,0,0,0,0,128,51200,56,72,1250000,1250000,512,1024,2.8,128,6,2</t>
-  </si>
-  <si>
-    <t>MAP-009,ETL_Cleansing_Mapper,ETL,100000000,32500000,1134,4536,32768,81,112,32500000,6500000,192,0,0,0,32500000,29800000,64,128,3.5,1536,15,5</t>
-  </si>
-  <si>
-    <t>RED-009,ETL_Cleansing_Reducer,ETL,32500000,15360000,504,2016,49152,0,0,0,0,192,76800,45,68,15360000,15360000,64,128,2.9,192,8,2</t>
-  </si>
-  <si>
-    <t>MAP-010,SearchIndex_Mapper,Indexing,25000000,25000000,189,756,12288,87,24,25000000,25000000,256,0,0,0,25000000,25000000,128,256,1.6,256,3,0</t>
-  </si>
-  <si>
-    <t>RED-010,SearchIndex_Reducer,Indexing,25000000,50000000,384,1536,24576,0,0,0,0,256,25600,56,89,50000000,50000000,128,256,1.7,128,4,1</t>
-  </si>
-  <si>
-    <t>MAP-011,SensorData_Mapper,IoT,15000000,5200000,44,176,4096,93,14,5200000,1250000,8,0,0,0,5200000,4800000,32,64,1.3,64,1,0</t>
-  </si>
-  <si>
-    <t>RED-011,SensorData_Reducer,IoT,5200000,3200000,29,116,4096,0,0,0,0,8,2100,6,12,3200000,3200000,32,64,1.2,8,1,0</t>
-  </si>
-  <si>
-    <t>MAP-012,SocialNet_Mapper,Graph,35000000,21700000,378,1512,24576,85,56,21700000,10800000,128,0,0,0,21700000,18900000,96,192,2.4,512,7,2</t>
-  </si>
-  <si>
-    <t>RED-012,SocialNet_Reducer,Graph,21700000,10800000,336,1344,32768,0,0,0,0,128,25600,42,58,10800000,10800000,96,192,2.2,128,5,1</t>
-  </si>
-  <si>
-    <t>MAP-013,Recommend_Mapper,ML,20000000,5400000,285,1140,16384,89,32,5400000,1800000,64,0,0,0,5400000,4850000,48,96,1.9,384,5,1</t>
-  </si>
-  <si>
-    <t>RED-013,Recommend_Reducer,ML,5400000,2560000,168,672,12288,0,0,0,0,64,19200,28,35,2560000,2560000,48,96,1.8,64,3,0</t>
-  </si>
-  <si>
-    <t>MAP-014,GenomeSeq_Mapper,Scientific,120000000,35000000,1512,6048,65536,78,145,35000000,12500000,256,0,0,0,35000000,31500000,256,512,4.2,2048,18,6</t>
-  </si>
-  <si>
-    <t>RED-014,GenomeSeq_Reducer,Scientific,35000000,10240000,672,2688,98304,0,0,0,0,256,89600,78,95,10240000,10240000,256,512,3.8,256,10,3</t>
-  </si>
-  <si>
-    <t>MAP-015,LogAnalytics_Mapper,Analytics,45000000,25800000,567,2268,20480,84,68,25800000,6300000,96,0,0,0,25800000,23500000,48,96,2.6,768,9,2</t>
-  </si>
-  <si>
-    <t>RED-015,LogAnalytics_Reducer,Analytics,25800000,12600000,252,1008,24576,0,0,0,0,96,38400,38,52,12600000,12600000,48,96,2.4,96,4,1</t>
-  </si>
-  <si>
-    <t>Q.No,Question,Stage_Concept,Analysis_Required,Expected_Answer,Key_Learning</t>
-  </si>
-  <si>
-    <t>1,"What is the Mapping stage in MapReduce? Explain its purpose and key activities using the dataset.","Mapping Stage Overview","Analyze MAP-* records for input/output, processing time","Mapping stage: Parallel processing of input splits. Input records: 5M-120M, Output records: 1.8M-35M (70% avg reduction). Processing time: 38-1512 sec","Mapping transforms raw input into intermediate key-value pairs"</t>
-  </si>
-  <si>
-    <t>2,"What is the Reducing stage in MapReduce? Explain its purpose and key activities using the dataset.","Reducing Stage Overview","Analyze RED-* records for aggregation and output","Reducing stage: Aggregates and processes mapped data. Input: 1.8M-35M records, Output: 320K-50M records. Processing: 15-672 sec","Reducing performs aggregation, summarization, and final output"</t>
-  </si>
-  <si>
-    <t>3,"What is the relationship between Map output and Reduce input? Analyze the data flow.","Map-Reduce Data Flow","Compare Map_Output_Records vs Reduce_Input_Records","Map output = Reduce input (100% transfer). Maps output 250K-35M records; Reducers receive exactly that data through shuffle","Shuffle phase transfers all map outputs to reducers"</t>
-  </si>
-  <si>
-    <t>4,"What is the reduction factor? Calculate the reduction from input to map output to reduce output.","Data Reduction","Calculate Input:Map_Output:Reduce_Output ratio","Input to Map: 100% input; Map output: 65% of input (35% reduction); Reduce output: 45% of map output (55% reduction); Overall: 70% reduction","Each stage reduces data volume, improving efficiency"</t>
-  </si>
-  <si>
-    <t>5,"What is data locality in mapping? Analyze map task data locality percentages.","Map Data Locality","Analyze Data_Local_Pct in mapping stage","Map data locality: 78-94% average 87%. Best: SalesAgg (94%), WordCount (92%), SensorData (93%); Lowest: GenomeSeq (78%), ImageProcess (82%)","High data locality (moving computation to data) is fundamental to MapReduce"</t>
-  </si>
-  <si>
-    <t>6,"What is spill in mapping? Explain spill count and its impact on performance.","Map Spill","Analyze Spill_Count in mapping stage","Spill count: 8-145 spills per job. Higher spills (145) for large jobs (GenomeSeq) indicate memory pressure. Spill to disk slows performance","Spills occur when map output exceeds memory buffer; minimize for better performance"</t>
-  </si>
-  <si>
-    <t>7,"What is the combiner in mapping? Analyze combiner efficiency from the dataset.","Combiner Optimization","Analyze Combine_Records_In vs Combine_Records_Out","Combiner reduces records: Input 1.2M-35M, Output 210K-12.5M. Reduction ratio: 2.5-6x (avg 4x). Most effective for aggregation jobs","Combiner performs local aggregation, reducing shuffle data volume"</t>
-  </si>
-  <si>
-    <t>8,"What is partitioning in reducing? Analyze partition count and its effect on parallelism.","Reduce Partitioning","Analyze Partition_Count in reduce stage","Partitions: 4-256. More partitions = more reducers = higher parallelism. Partition count should match number of reduce tasks","Partitioner determines which reducer processes each key"</t>
-  </si>
-  <si>
-    <t>9,"What is shuffle data size? Analyze shuffle volume and its relationship to reduce performance.","Shuffle Phase","Analyze Shuffle_Data_MB in reduce stage","Shuffle data: 1.8-89.6 GB per job. Larger shuffle (89.6GB for GenomeSeq) increases reduce time (672 sec) and network load","Shuffle is most network-intensive; optimize with combiner and compression"</t>
-  </si>
-  <si>
-    <t>10,"What is sort time in reducing? Analyze sort time as percentage of reduce time.","Reduce Sorting","Analyze Sort_Time_Sec vs Reduce_Time_Sec","Sort time: 5-78 sec (15-25% of reduce time). Sort is required to group keys before reduction","Hadoop sorts map outputs by key; sort time increases with data volume"</t>
-  </si>
-  <si>
-    <t>11,"What is grouping time in reducing? Analyze group time and its relationship to key count.","Reduce Grouping","Analyze Group_Time_Sec vs Key_Count","Group time: 10-95 sec. Higher key counts (50M for SearchIndex) increase grouping time. Grouping assembles all values for each key","Grouping organizes all values with same key for reduce function"</t>
-  </si>
-  <si>
-    <t>12,"What is key count and unique keys? Analyze key distribution across jobs.","Key Distribution","Analyze Key_Count vs Unique_Keys","Total keys: 320K-50M; Unique keys: 85-95% of total keys. High uniqueness (95% for WordCount) indicates many distinct keys","Key distribution affects reducer load; high skew can cause performance issues"</t>
-  </si>
-  <si>
-    <t>13,"What is skew factor? Identify jobs with high data skew and its impact.","Data Skew","Analyze Skew_Factor in map and reduce stages","Skew factor: 1.1-4.2. High skew (&gt;2.5): FraudDetect (2.8), ImageProcess (3.2), GenomeSeq (4.2). Causes uneven reducer load","Data skew causes some reducers to process much more data than others"</t>
-  </si>
-  <si>
-    <t>14,"What is the difference between map tasks and reduce tasks? Compare their counts and resource usage.","Task Comparison","Compare Map_Task_Count vs Reduce_Task_Count","Map tasks: 64-2048 (avg 512); Reduce tasks: 8-256 (avg 72). Maps have higher parallelism (8:1 ratio)","Maps scale with input splits; reduces scale with output partitions"</t>
-  </si>
-  <si>
-    <t>15,"What is speculative execution? Analyze speculative runs and failed attempts.","Speculative Execution","Analyze Speculative_Runs, Failed_Attempts","Speculative runs: 1-18 per job; Failed attempts: 0-6. GenomeSeq had 18 speculative runs, 6 failures. Handles stragglers","Speculative execution duplicates slow tasks; prevents job delays"</t>
-  </si>
-  <si>
-    <t>16,"What is average key and value size? Analyze how data characteristics affect performance.","Key-Value Characteristics","Analyze Avg_Key_Size_Bytes, Avg_Value_Size_Bytes","Key size: 12-512 bytes; Value size: 24-1024 bytes. Large values (ImageProcess 1024 bytes) increase shuffle data","Key-value sizes impact memory usage and shuffle time"</t>
-  </si>
-  <si>
-    <t>17,"What is processing time vs CPU time? Analyze parallelism efficiency.","Processing Efficiency","Compare Processing_Time_Sec vs CPU_Time_Sec","Processing time: 38-1512 sec (map), 15-672 sec (reduce). CPU time: 4x processing time (parallelism across cores)","CPU time &gt; wall time indicates parallel execution across multiple cores"</t>
-  </si>
-  <si>
-    <t>18,"What is memory usage in mapping vs reducing? Compare memory requirements.","Memory Analysis","Compare Memory_MB in map vs reduce stages","Map memory: 4-65 GB (avg 18 GB); Reduce memory: 4-98 GB (avg 24 GB). Reduce requires 30% more memory","Reduce phase often requires more memory for aggregation and sorting"</t>
-  </si>
-  <si>
-    <t>19,"What are the different job types and their mapping characteristics? Analyze job patterns.","Job Type Patterns","Group by Job_Type; analyze metrics","ETL: High input (100M), moderate output (32.5M); Analytics: Balanced; Aggregation: High reduction; Graph: 1:1 map-reduce ratio","Different job types have distinct MapReduce patterns and optimizations"</t>
-  </si>
-  <si>
-    <t>20,"Create a MapReduce stage summary with key metrics: map efficiency, reduce efficiency, overall throughput.","Stage Summary","Calculate summary metrics across all jobs","Map: 87% data locality, 4x combiner reduction, 512 avg tasks; Reduce: 72 tasks, 2.8x CPU factor, 85% success; Overall: 70% data reduction","MapReduce stages work together to process massive datasets efficiently"</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -199,33 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,285 +316,963 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Row_ID,Order_ID,Order_Date,Sales_Amount,Quantity,Profit,Discount,Product_Category,Product_Name,Customer_Age,Customer_Segment,Order_Priority,Shipping_Days,Delivery_Status,Return_Flag,Satisfaction_Score,Units_Ordered,Unit_Price,Shipping_Cost,Payment_Terms</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>1,ORD-1001,2024-01-05,1299.99,1,389.99,0.05,Electronics,MacBook Pro,45,Corporate,High,3,Delivered,FALSE,4.8,1,1299.99,15.00,Net30</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>2,ORD-1002,2024-01-05,79.99,3,23.99,0.10,Electronics,Magic Mouse,45,Corporate,Medium,2,Delivered,FALSE,4.5,3,26.66,8.50,Net30</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>3,ORD-1003,2024-01-06,89.99,2,26.99,0.00,Clothing,Designer Jeans,28,Consumer,Medium,4,Delivered,FALSE,4.2,2,44.99,12.00,COD</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>4,ORD-1004,2024-01-06,299.99,1,89.99,0.15,Electronics,27-inch Monitor,32,Consumer,High,3,Delivered,FALSE,4.9,1,299.99,18.00,Net15</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>5</v>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>5,ORD-1005,2024-01-07,399.99,2,119.99,0.05,Furniture,Executive Chair,52,Corporate,High,5,Delivered,FALSE,5.0,2,199.99,22.00,Net30</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>6,ORD-1006,2024-01-07,89.99,2,26.99,0.10,Electronics,Mechanical Keyboard,26,Consumer,Low,3,Delayed,FALSE,3.5,2,44.99,10.00,COD</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>7,ORD-1007,2024-01-08,199.99,1,59.99,0.20,Clothing,Leather Jacket,34,Home Office,Medium,4,Delivered,FALSE,4.7,1,199.99,15.00,Net15</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>8</v>
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>8,ORD-1008,2024-01-08,499.99,1,149.99,0.05,Electronics,iPad,41,Corporate,High,2,Delivered,FALSE,4.9,1,499.99,20.00,Net30</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>9</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>9,ORD-1009,2024-01-09,79.99,2,23.99,0.00,Furniture,Floor Lamp,38,Consumer,Low,3,Delivered,FALSE,4.0,2,39.99,12.00,COD</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>10</v>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>10,ORD-1010,2024-01-09,69.99,1,20.99,0.10,Clothing,Running Shoes,29,Consumer,Medium,2,Returned,TRUE,2.8,1,69.99,10.00,COD</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>11</v>
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>11,ORD-1011,2024-01-10,1299.99,1,389.99,0.15,Electronics,Gaming Laptop,35,Corporate,High,4,Delivered,FALSE,5.0,1,1299.99,25.00,Net30</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>12</v>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12,ORD-1012,2024-01-10,149.99,2,44.99,0.05,Electronics,Headphones,27,Consumer,Medium,3,Delivered,FALSE,4.3,2,74.99,12.00,Net15</t>
+        </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>13,ORD-1013,2024-01-11,189.99,1,56.99,0.20,Clothing,Wool Coat,39,Home Office,Medium,4,Delivered,FALSE,4.5,1,189.99,15.00,Net15</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>14</v>
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>14,ORD-1014,2024-01-11,159.99,1,47.99,0.10,Furniture,Bookshelf,47,Corporate,Medium,5,Delivered,FALSE,4.2,1,159.99,18.00,Net30</t>
+        </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>15,ORD-1015,2024-01-12,699.99,2,209.99,0.05,Electronics,Smartphone,31,Consumer,High,3,Delivered,FALSE,4.8,2,349.99,12.00,COD</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>16</v>
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>16,ORD-1016,2024-01-12,59.99,3,17.99,0.00,Clothing,Dress Shirt,44,Corporate,Medium,2,Delivered,FALSE,4.4,3,20.00,10.00,Net30</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>17</v>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>17,ORD-1017,2024-01-13,99.99,1,29.99,0.10,Electronics,External SSD,33,Consumer,Low,3,Delivered,FALSE,3.9,1,99.99,8.50,COD</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>18</v>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>18,ORD-1018,2024-01-13,49.99,2,14.99,0.05,Clothing,Hoodie,25,Consumer,Medium,2,Returned,TRUE,2.5,2,25.00,12.00,COD</t>
+        </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>19</v>
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>19,ORD-1019,2024-01-14,349.99,1,104.99,0.15,Furniture,Gaming Desk,42,Corporate,High,4,Delivered,FALSE,4.9,1,349.99,25.00,Net30</t>
+        </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>20</v>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>20,ORD-1020,2024-01-14,79.99,2,23.99,0.10,Electronics,Webcam,36,Home Office,Medium,3,Delivered,FALSE,4.6,2,39.99,8.50,Net15</t>
+        </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="s">
-        <v>21</v>
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>21,ORD-1021,2024-02-01,129.99,1,38.99,0.00,Electronics,Docking Station,40,Consumer,Low,3,Delivered,FALSE,4.1,1,129.99,10.00,COD</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="s">
-        <v>22</v>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>22,ORD-1022,2024-02-01,179.99,1,53.99,0.05,Clothing,Winter Parka,48,Consumer,Medium,4,Delivered,FALSE,4.3,1,179.99,15.00,COD</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>23</v>
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>23,ORD-1023,2024-02-02,449.99,1,134.99,0.10,Furniture,Office Desk,53,Corporate,High,5,Delivered,FALSE,4.9,1,449.99,22.00,Net30</t>
+        </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>24,ORD-1024,2024-02-02,39.99,3,11.99,0.00,Electronics,USB-C Hub,24,Consumer,Low,2,Delivered,FALSE,3.8,3,13.33,8.50,COD</t>
+        </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="s">
-        <v>25</v>
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>25,ORD-1025,2024-02-03,149.99,1,44.99,0.15,Clothing,Casual Blazer,37,Home Office,Medium,3,Delivered,FALSE,4.7,1,149.99,12.00,Net15</t>
+        </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="s">
-        <v>26</v>
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>26,ORD-1026,2024-02-03,59.99,2,17.99,0.10,Electronics,Gaming Mouse,22,Consumer,Medium,2,Returned,TRUE,2.9,2,29.99,8.50,COD</t>
+        </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="s">
-        <v>27</v>
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>27,ORD-1027,2024-02-04,199.99,1,59.99,0.05,Electronics,Laser Printer,49,Corporate,High,4,Delivered,FALSE,4.8,1,199.99,18.00,Net30</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="s">
-        <v>28</v>
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>28,ORD-1028,2024-02-04,279.99,1,83.99,0.20,Furniture,Lounge Chair,56,Consumer,Medium,5,Delivered,FALSE,4.2,1,279.99,22.00,Net15</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="s">
-        <v>29</v>
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>29,ORD-1029,2024-02-05,49.99,4,14.99,0.00,Electronics,Power Bank,30,Consumer,Low,2,Delivered,FALSE,4.0,4,12.50,8.50,COD</t>
+        </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="s">
-        <v>30</v>
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>30,ORD-1030,2024-02-05,24.99,5,7.49,0.10,Clothing,Wool Scarf,26,Consumer,Medium,2,Delivered,FALSE,4.1,5,5.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>31,ORD-1031,2024-02-06,119.99,1,35.99,0.05,Electronics,Gaming Headset,34,Corporate,High,3,Delivered,FALSE,4.9,1,119.99,12.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>32,ORD-1032,2024-02-06,69.99,2,20.99,0.10,Furniture,Night Stand,44,Home Office,Medium,3,Delivered,FALSE,4.3,2,34.99,15.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>33,ORD-1033,2024-02-07,109.99,1,32.99,0.15,Clothing,Athletic Shoes,29,Consumer,Medium,2,Delivered,FALSE,4.5,1,109.99,10.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>34,ORD-1034,2024-02-07,199.99,1,59.99,0.05,Electronics,Smart Watch,38,Consumer,High,3,Delivered,FALSE,4.7,1,199.99,12.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>35,ORD-1035,2024-02-08,79.99,2,23.99,0.10,Electronics,Bluetooth Speaker,31,Corporate,Medium,3,Delivered,FALSE,4.4,2,39.99,10.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>36,ORD-1036,2024-02-08,99.99,1,29.99,0.00,Clothing,Cashmere Sweater,41,Consumer,Low,3,Returned,TRUE,2.7,1,99.99,12.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>37,ORD-1037,2024-02-09,129.99,1,38.99,0.05,Furniture,Bookshelf,46,Home Office,Medium,4,Delivered,FALSE,4.2,1,129.99,18.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>38,ORD-1038,2024-02-09,99.99,1,29.99,0.10,Electronics,Mesh Router,28,Consumer,Low,2,Delivered,FALSE,4.0,1,99.99,10.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>39,ORD-1039,2024-02-10,44.99,3,13.49,0.15,Clothing,Golf Polo,23,Consumer,Medium,2,Delivered,FALSE,4.3,3,15.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>40,ORD-1040,2024-02-10,499.99,1,149.99,0.20,Electronics,Graphics Card,43,Corporate,High,4,Delivered,FALSE,5.0,1,499.99,18.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>41,ORD-1041,2024-03-01,999.99,1,299.99,0.05,Electronics,Desktop PC,50,Corporate,High,3,Delivered,FALSE,4.9,1,999.99,25.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>42,ORD-1042,2024-03-01,49.99,2,14.99,0.00,Clothing,Yoga Pants,27,Consumer,Medium,2,Delivered,FALSE,4.4,2,25.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>43,ORD-1043,2024-03-02,249.99,1,74.99,0.10,Furniture,Coffee Table,55,Corporate,High,4,Delivered,FALSE,4.8,1,249.99,22.00,Net30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>44,ORD-1044,2024-03-02,89.99,2,26.99,0.00,Electronics,Smart Speaker,34,Home Office,Medium,2,Delivered,FALSE,4.6,2,45.00,10.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>45,ORD-1045,2024-03-03,19.99,4,5.99,0.05,Clothing,Baseball Cap,19,Consumer,Low,2,Delivered,FALSE,3.5,4,5.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>46,ORD-1046,2024-03-03,349.99,1,104.99,0.10,Electronics,Quadcopter,38,Consumer,High,3,Delivered,FALSE,4.9,1,349.99,18.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>47,ORD-1047,2024-03-04,59.99,2,17.99,0.00,Furniture,Wall Mirror,42,Consumer,Medium,2,Delivered,FALSE,4.2,2,30.00,12.00,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>48,ORD-1048,2024-03-04,49.99,2,14.99,0.10,Clothing,Flannel Shirt,35,Home Office,Medium,3,Delivered,FALSE,4.1,2,25.00,10.00,Net15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>49,ORD-1049,2024-03-05,29.99,3,8.99,0.05,Electronics,Streaming Stick,24,Consumer,Low,2,Returned,TRUE,2.6,3,10.00,8.50,COD</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>50,ORD-1050,2024-03-05,29.99,4,8.99,0.00,Clothing,Leggings,22,Consumer,Medium,2,Delivered,FALSE,4.3,4,7.50,8.50,COD</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>31</v>
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>32</v>
-      </c>
+      <c r="A2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Sales_Tier' that categorizes Sales_Amount: &gt;1000 = 'Premium', 500-1000 = 'High', 200-500 = 'Medium', &lt;200 = 'Low'</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr"/>
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>33</v>
-      </c>
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Profit_Status' based on Profit: &gt;100 = 'Highly Profitable', &gt;0 = 'Profitable', =0 = 'Break Even', &lt;0 = 'Loss'</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr"/>
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
-        <v>34</v>
-      </c>
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Order_Size' that categorizes Quantity: &gt;5 = 'Bulk Order', 3-5 = 'Standard Order', 1-2 = 'Small Order'</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr"/>
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Customer_Age_Group' based on Customer_Age: &lt;30 = 'Young', 30-50 = 'Middle', &gt;50 = 'Senior'</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Discount_Level' based on Discount: 0 = 'No Discount', 0.01-0.10 = 'Low Discount', 0.11-0.20 = 'High Discount'</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Shipping_Performance' based on Shipping_Days: &lt;=2 = 'Fast', 3-4 = 'Normal', &gt;=5 = 'Slow'</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
+      <c r="A8" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Delivery_Status_Text' that converts Delivery_Status: 'Delivered' = 'On Time', 'Delayed' = 'Late', 'Returned' = 'Returned'</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr"/>
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
+      <c r="A9" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Customer_Value' based on Sales_Amount and Quantity: If Sales_Amount &gt; 500 AND Quantity &gt; 1 then 'High Value', else 'Standard'</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr"/>
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Premium_Customer' based on Customer_Segment OR Order_Priority: If Corporate OR High then 'Premium', else 'Regular'</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr"/>
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>41</v>
-      </c>
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Return_Risk' based on multiple conditions: If Discount &gt; 0.15 OR Satisfaction_Score &lt; 3 then 'High Risk', else 'Low Risk'</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr"/>
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
-        <v>42</v>
-      </c>
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Order_Profitability' based on Profit and Quantity: If Profit &gt; 100 AND Quantity &gt; 1 then 'High', if Profit &gt; 50 then 'Medium', else 'Low'</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr"/>
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
-        <v>43</v>
-      </c>
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Shipping_Cost_Category' based on Shipping_Cost: &lt;10 = 'Low Cost', 10-20 = 'Medium Cost', &gt;20 = 'High Cost'</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
-        <v>44</v>
-      </c>
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Product_Priority' based on Category AND Order_Priority: If Electronics AND High then 'Urgent', else 'Normal'</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
-        <v>45</v>
-      </c>
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Payment_Risk' based on Payment_Terms: If COD then 'High Risk', if Net15 then 'Medium Risk', if Net30 then 'Low Risk'</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
-        <v>46</v>
-      </c>
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Sales_Efficiency' based on Units_Ordered and Unit_Price: If Units_Ordered &gt; 2 AND Unit_Price &gt; 100 then 'Efficient', else 'Standard'</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>47</v>
-      </c>
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Return_Flag_Text' that converts Return_Flag: TRUE = 'Returned', FALSE = 'Not Returned'</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
-        <v>48</v>
-      </c>
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Order_Value_Index' that uses a SWITCH function to assign values: 0-100 = 1, 101-500 = 2, 501-1000 = 3, &gt;1000 = 4</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
-        <v>49</v>
-      </c>
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Season' based on Order_Date month: 12,1,2 = 'Winter', 3,4,5 = 'Spring', 6,7,8 = 'Summer', 9,10,11 = 'Fall'</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr"/>
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Bulk_Discount_Flag' that checks if Quantity &gt; 5 AND Discount &gt; 0.05 THEN 'Eligible' ELSE 'Not Eligible'</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Creating Conditional Columns</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a Conditional Column named 'Customer_Tier' using nested IF with Customer_Segment, Satisfaction_Score, and Sales_Amount: If Corporate and Satisfaction &gt; 4.5 and Sales &gt; 500 then 'Platinum', if Corporate or Sales &gt; 500 then 'Gold', else 'Standard'</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>